--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5461,4 +5462,176 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. WM - Monitor Arm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5755</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="n">
+        <v>497.77</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. WM - Monitor Arm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11172</v>
+      </c>
+      <c r="E3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1974.52</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15291.52</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1. WM - Monitor Arm</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11668</v>
+      </c>
+      <c r="E4" t="n">
+        <v>115</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2311.92</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9344.059999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -5470,7 +5470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5631,6 +5631,191 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2. WM - L Shape</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6200.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>580.570345</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20993.645</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. WM - L Shape</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6200.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>580.570345</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20993.645</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3. WM - Desk - Manual</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0CPT3Q25C</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2362.333333333333</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.33333333333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>295.8679633333333</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4237.57</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3. WM - Desk - Manual</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0DQ1NV8D2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2362.333333333333</v>
+      </c>
+      <c r="E8" t="n">
+        <v>45.33333333333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>295.8679633333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4237.57</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3. WM - Desk - Manual</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DQ4YWSMC</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2362.333333333333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45.33333333333334</v>
+      </c>
+      <c r="F9" t="n">
+        <v>295.8679633333333</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4237.57</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6200.5</v>
+        <v>6200</v>
       </c>
       <c r="E5" t="n">
-        <v>265.5</v>
+        <v>266</v>
       </c>
       <c r="F5" t="n">
         <v>580.570345</v>
@@ -4397,7 +4397,7 @@
         <v>20993.645</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4422,10 +4422,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6200.5</v>
+        <v>6200</v>
       </c>
       <c r="E6" t="n">
-        <v>265.5</v>
+        <v>266</v>
       </c>
       <c r="F6" t="n">
         <v>580.570345</v>
@@ -4434,7 +4434,7 @@
         <v>20993.645</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2362.333333333333</v>
+        <v>2362</v>
       </c>
       <c r="E7" t="n">
-        <v>45.33333333333334</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
         <v>295.8679633333333</v>
@@ -4471,7 +4471,7 @@
         <v>4237.57</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2362.333333333333</v>
+        <v>2362</v>
       </c>
       <c r="E8" t="n">
-        <v>45.33333333333334</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
         <v>295.8679633333333</v>
@@ -4508,7 +4508,7 @@
         <v>4237.57</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2362.333333333333</v>
+        <v>2362</v>
       </c>
       <c r="E9" t="n">
-        <v>45.33333333333334</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
         <v>295.8679633333333</v>
@@ -4545,7 +4545,7 @@
         <v>4237.57</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,46 +415,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -575,7 +563,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>455</v>
+        <v>406</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -597,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>938.5500000000001</v>
+        <v>814.1900000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>9830</v>
+        <v>7943</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,19 +613,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3982.03</v>
+        <v>3332.55</v>
       </c>
       <c r="E7" t="n">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="F7" t="n">
-        <v>57680</v>
+        <v>48170</v>
       </c>
       <c r="G7" t="n">
-        <v>28188.58</v>
+        <v>14122.47</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -653,13 +641,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>710.61</v>
+        <v>538.24</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>7900</v>
+        <v>5144</v>
       </c>
       <c r="G8" t="n">
         <v>14617.8</v>
@@ -681,13 +669,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>511.4</v>
+        <v>323.48</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>1270</v>
+        <v>989</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -709,13 +697,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>536.72</v>
+        <v>453.96</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>4620</v>
+        <v>3584</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -849,13 +837,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2356.75</v>
+        <v>2163.34</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
-        <v>27710</v>
+        <v>25387</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -877,13 +865,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>698.46</v>
+        <v>636.36</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" t="n">
-        <v>4195</v>
+        <v>3780</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -905,13 +893,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>341.85</v>
+        <v>324.08</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>2682</v>
+        <v>2061</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -933,13 +921,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3547.11</v>
+        <v>3100.16</v>
       </c>
       <c r="E18" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>54681</v>
+        <v>36753</v>
       </c>
       <c r="G18" t="n">
         <v>7046.62</v>
@@ -961,19 +949,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>176.25</v>
+        <v>159.14</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>3449</v>
+        <v>2909</v>
       </c>
       <c r="G19" t="n">
-        <v>6761.86</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -995,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1045,13 +1033,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>59.19</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1073,13 +1061,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>773.1700000000001</v>
+        <v>669.04</v>
       </c>
       <c r="E23" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>14511</v>
+        <v>10035</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1101,13 +1089,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>312.3</v>
+        <v>186.9</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>4096</v>
+        <v>2638</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1129,13 +1117,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1083.6</v>
+        <v>984.9200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F25" t="n">
-        <v>8650</v>
+        <v>7796</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1157,13 +1145,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2964.29</v>
+        <v>2691.92</v>
       </c>
       <c r="E26" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F26" t="n">
-        <v>44180</v>
+        <v>40067</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1185,13 +1173,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>401.19</v>
+        <v>290.05</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>6344</v>
+        <v>3064</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1213,19 +1201,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>421.52</v>
+        <v>332.79</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>13370</v>
+        <v>11506</v>
       </c>
       <c r="G28" t="n">
-        <v>31247.47</v>
+        <v>10168.64</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1241,13 +1229,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>579.76</v>
+        <v>488.81</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>2152</v>
+        <v>2036</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1269,19 +1257,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2355.62</v>
+        <v>2084.43</v>
       </c>
       <c r="E30" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="F30" t="n">
-        <v>14155</v>
+        <v>12294</v>
       </c>
       <c r="G30" t="n">
-        <v>6761.86</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1297,19 +1285,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1769.67</v>
+        <v>1577.84</v>
       </c>
       <c r="E31" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F31" t="n">
-        <v>7665</v>
+        <v>6800</v>
       </c>
       <c r="G31" t="n">
-        <v>20760.18</v>
+        <v>13727.12</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1325,13 +1313,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1338.33</v>
+        <v>1183.97</v>
       </c>
       <c r="E32" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="F32" t="n">
-        <v>15416</v>
+        <v>11645</v>
       </c>
       <c r="G32" t="n">
         <v>13896.61</v>
@@ -1353,19 +1341,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1283.12</v>
+        <v>1202.8</v>
       </c>
       <c r="E33" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F33" t="n">
-        <v>3606</v>
+        <v>3284</v>
       </c>
       <c r="G33" t="n">
-        <v>14049.15</v>
+        <v>21251.69</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1381,13 +1369,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>546.1799999999999</v>
+        <v>420.8</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>3567</v>
+        <v>2856</v>
       </c>
       <c r="G34" t="n">
         <v>12712.71</v>
@@ -1409,13 +1397,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>466.39</v>
+        <v>410.56</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F35" t="n">
-        <v>4829</v>
+        <v>4698</v>
       </c>
       <c r="G35" t="n">
         <v>21845.76</v>
@@ -1437,13 +1425,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>243.15</v>
+        <v>153.9</v>
       </c>
       <c r="E36" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>2872</v>
+        <v>2754</v>
       </c>
       <c r="G36" t="n">
         <v>10778.82</v>
@@ -1471,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>320</v>
+        <v>121</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1493,13 +1481,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1141.7</v>
+        <v>1062.15</v>
       </c>
       <c r="E38" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F38" t="n">
-        <v>48939</v>
+        <v>47853</v>
       </c>
       <c r="G38" t="n">
         <v>10066.96</v>
@@ -1521,13 +1509,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>119.85</v>
+        <v>96.13999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>3305</v>
+        <v>2656</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1549,13 +1537,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7589.05</v>
+        <v>6688.25</v>
       </c>
       <c r="E40" t="n">
-        <v>500</v>
+        <v>444</v>
       </c>
       <c r="F40" t="n">
-        <v>74566</v>
+        <v>59152</v>
       </c>
       <c r="G40" t="n">
         <v>13727.12</v>
@@ -1568,22 +1556,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SP CT PT_B0CPFS24ML_Gaming</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>325.81</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3688</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1601,17 +1589,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>386.78</v>
+        <v>20.78</v>
       </c>
       <c r="E42" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>5700</v>
+        <v>303</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1629,51 +1617,51 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20.78</v>
+        <v>198.31</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F43" t="n">
-        <v>408</v>
+        <v>3324</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>7117.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>276.92</v>
+        <v>666.6900000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>4285</v>
+        <v>2881</v>
       </c>
       <c r="G44" t="n">
-        <v>7117.8</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1685,58 +1673,58 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>805.9</v>
+        <v>534.51</v>
       </c>
       <c r="E45" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>3476</v>
+        <v>4429</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>7046.62</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>WB- SP- B0DB5VG39T - CT ref</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>612.65</v>
+        <v>724.66</v>
       </c>
       <c r="E46" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F46" t="n">
-        <v>6058</v>
+        <v>5117</v>
       </c>
       <c r="G46" t="n">
-        <v>7046.62</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - CT ref</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1745,47 +1733,47 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>886.78</v>
+        <v>1157.57</v>
       </c>
       <c r="E47" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>6250</v>
+        <v>7357</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1360.08</v>
+        <v>443.63</v>
       </c>
       <c r="E48" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="F48" t="n">
-        <v>8758</v>
+        <v>2940</v>
       </c>
       <c r="G48" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1797,17 +1785,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>536.3099999999999</v>
+        <v>1276.77</v>
       </c>
       <c r="E49" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="F49" t="n">
-        <v>3316</v>
+        <v>5565</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1820,162 +1808,162 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1415.94</v>
+        <v>1501.36</v>
       </c>
       <c r="E50" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F50" t="n">
-        <v>6385</v>
+        <v>2844</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>5370.34</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1720.33</v>
+        <v>378.5</v>
       </c>
       <c r="E51" t="n">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="F51" t="n">
-        <v>3253</v>
+        <v>390</v>
       </c>
       <c r="G51" t="n">
-        <v>7149.15</v>
+        <v>2456.78</v>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>443.77</v>
+        <v>623.8100000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>435</v>
+        <v>5034</v>
       </c>
       <c r="G52" t="n">
-        <v>2456.78</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>739.58</v>
+        <v>953.1799999999998</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F53" t="n">
-        <v>5898</v>
+        <v>7953</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>WB- SP-B0DP3194QN-PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1146.29</v>
+        <v>275.83</v>
       </c>
       <c r="E54" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="F54" t="n">
-        <v>9825</v>
+        <v>1291</v>
       </c>
       <c r="G54" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WB- SP-B0DP3194QN-PT</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>334.18</v>
+        <v>720</v>
       </c>
       <c r="E55" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F55" t="n">
-        <v>1517</v>
+        <v>10245</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1988,53 +1976,53 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>720</v>
+        <v>549.1700000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F56" t="n">
-        <v>10245</v>
+        <v>24714</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>549.1700000000001</v>
+        <v>1357.97</v>
       </c>
       <c r="E57" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="F57" t="n">
-        <v>24719</v>
+        <v>23351</v>
       </c>
       <c r="G57" t="n">
-        <v>2626.27</v>
+        <v>1795.76</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
@@ -2044,35 +2032,35 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1357.97</v>
+        <v>2241.8</v>
       </c>
       <c r="E58" t="n">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="F58" t="n">
-        <v>23351</v>
+        <v>28486</v>
       </c>
       <c r="G58" t="n">
-        <v>1795.76</v>
+        <v>7416.96</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2081,47 +2069,47 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2241.8</v>
+        <v>863.6499999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="F59" t="n">
-        <v>28487</v>
+        <v>1015</v>
       </c>
       <c r="G59" t="n">
-        <v>7416.96</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1037.19</v>
+        <v>723.4000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F60" t="n">
-        <v>1158</v>
+        <v>2866</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2791.52</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2133,30 +2121,30 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>823.9300000000001</v>
+        <v>903.6700000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F61" t="n">
-        <v>3196</v>
+        <v>2720</v>
       </c>
       <c r="G61" t="n">
-        <v>2791.52</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2165,110 +2153,110 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>948.9</v>
+        <v>716.37</v>
       </c>
       <c r="E62" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F62" t="n">
-        <v>3101</v>
+        <v>5155</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>5082.209999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>863.24</v>
+        <v>449.46</v>
       </c>
       <c r="E63" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F63" t="n">
-        <v>6910</v>
+        <v>2991</v>
       </c>
       <c r="G63" t="n">
-        <v>5082.209999999999</v>
+        <v>4913.56</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>642.67</v>
+        <v>1407.38</v>
       </c>
       <c r="E64" t="n">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="F64" t="n">
-        <v>4021</v>
+        <v>6080</v>
       </c>
       <c r="G64" t="n">
-        <v>4913.56</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1564.94</v>
+        <v>2879.83</v>
       </c>
       <c r="E65" t="n">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="F65" t="n">
-        <v>6604</v>
+        <v>8520</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>31972.04</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2277,26 +2265,26 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3358.73</v>
+        <v>1834.73</v>
       </c>
       <c r="E66" t="n">
-        <v>199</v>
+        <v>92</v>
       </c>
       <c r="F66" t="n">
-        <v>9963</v>
+        <v>3251</v>
       </c>
       <c r="G66" t="n">
-        <v>34428.82</v>
+        <v>2711.02</v>
       </c>
       <c r="H66" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2305,26 +2293,26 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2114.52</v>
+        <v>5027.3</v>
       </c>
       <c r="E67" t="n">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="F67" t="n">
-        <v>3660</v>
+        <v>18858</v>
       </c>
       <c r="G67" t="n">
-        <v>2711.02</v>
+        <v>17197.46</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2333,131 +2321,131 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5776.28</v>
+        <v>2473.27</v>
       </c>
       <c r="E68" t="n">
-        <v>291</v>
+        <v>158</v>
       </c>
       <c r="F68" t="n">
-        <v>22791</v>
+        <v>31635</v>
       </c>
       <c r="G68" t="n">
-        <v>24567.8</v>
+        <v>2456.78</v>
       </c>
       <c r="H68" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2473.27</v>
+        <v>402.01</v>
       </c>
       <c r="E69" t="n">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="F69" t="n">
-        <v>31640</v>
+        <v>11232</v>
       </c>
       <c r="G69" t="n">
-        <v>2456.78</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>402.01</v>
+        <v>1714.15</v>
       </c>
       <c r="E70" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F70" t="n">
-        <v>11232</v>
+        <v>8925</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2215.26</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1714.15</v>
+        <v>1345.26</v>
       </c>
       <c r="E71" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F71" t="n">
-        <v>8925</v>
+        <v>13406</v>
       </c>
       <c r="G71" t="n">
-        <v>2215.26</v>
+        <v>3388.13</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1345.26</v>
+        <v>517.5700000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="F72" t="n">
-        <v>13406</v>
+        <v>15001</v>
       </c>
       <c r="G72" t="n">
-        <v>3388.13</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2469,17 +2457,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>517.5700000000001</v>
+        <v>416.7</v>
       </c>
       <c r="E73" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
-        <v>15400</v>
+        <v>2684</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2497,17 +2485,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>416.7</v>
+        <v>245.67</v>
       </c>
       <c r="E74" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F74" t="n">
-        <v>2793</v>
+        <v>2684</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2525,17 +2513,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>320.26</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>2785</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2553,17 +2541,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>434.67</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>10965</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2581,17 +2569,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>451.26</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>11125</v>
+        <v>3</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2609,17 +2597,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>19.65</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>34</v>
+        <v>2809</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2632,22 +2620,22 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>19.65</v>
+        <v>172.08</v>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>2811</v>
+        <v>870</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2665,23 +2653,23 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>172.08</v>
+        <v>320.56</v>
       </c>
       <c r="E80" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F80" t="n">
-        <v>894</v>
+        <v>1482</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2693,23 +2681,23 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>331.04</v>
+        <v>483.99</v>
       </c>
       <c r="E81" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F81" t="n">
-        <v>1559</v>
+        <v>3814</v>
       </c>
       <c r="G81" t="n">
-        <v>1694.07</v>
+        <v>4841.52</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2721,23 +2709,23 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>569.13</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4726</v>
+        <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>4841.52</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2749,51 +2737,51 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>100.02</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F83" t="n">
-        <v>54</v>
+        <v>875</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>100.02</v>
+        <v>851.11</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F84" t="n">
-        <v>1129</v>
+        <v>18772</v>
       </c>
       <c r="G84" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2805,17 +2793,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>918.95</v>
+        <v>1523.41</v>
       </c>
       <c r="E85" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F85" t="n">
-        <v>19486</v>
+        <v>23549</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2828,22 +2816,22 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1670.5</v>
+        <v>195.08</v>
       </c>
       <c r="E86" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="F86" t="n">
-        <v>25073</v>
+        <v>8261</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2861,51 +2849,51 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>195.08</v>
+        <v>1080.15</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>8438</v>
+        <v>21600</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1182.5</v>
+        <v>1777.91</v>
       </c>
       <c r="E88" t="n">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="F88" t="n">
-        <v>22663</v>
+        <v>39357</v>
       </c>
       <c r="G88" t="n">
-        <v>2626.27</v>
+        <v>17143.22</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -2917,58 +2905,58 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1899.13</v>
+        <v>158.36</v>
       </c>
       <c r="E89" t="n">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="F89" t="n">
-        <v>40103</v>
+        <v>2211</v>
       </c>
       <c r="G89" t="n">
-        <v>17143.22</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>186.53</v>
+        <v>932.27</v>
       </c>
       <c r="E90" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="F90" t="n">
-        <v>2709</v>
+        <v>12509</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>9089.83</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2977,26 +2965,26 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1362.54</v>
+        <v>2198.2</v>
       </c>
       <c r="E91" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F91" t="n">
-        <v>18730</v>
+        <v>7421</v>
       </c>
       <c r="G91" t="n">
-        <v>9089.83</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3005,13 +2993,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2335.67</v>
+        <v>710.29</v>
       </c>
       <c r="E92" t="n">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="F92" t="n">
-        <v>8570</v>
+        <v>744</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3029,17 +3017,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>710.29</v>
+        <v>697.51</v>
       </c>
       <c r="E93" t="n">
         <v>17</v>
       </c>
       <c r="F93" t="n">
-        <v>802</v>
+        <v>637</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3052,22 +3040,22 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>748.1800000000001</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>726</v>
+        <v>7</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3080,7 +3068,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3089,13 +3077,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>221.91</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>737</v>
+        <v>40</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3108,7 +3096,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3117,13 +3105,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>171.98</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3136,56 +3124,56 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>68.01000000000001</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>4549</v>
+        <v>19</v>
       </c>
       <c r="G97" t="n">
-        <v>2388.98</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>20</v>
+        <v>2431</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>655.08</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -3197,23 +3185,23 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>299.29</v>
+        <v>650.27</v>
       </c>
       <c r="E99" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F99" t="n">
-        <v>2621</v>
+        <v>6570</v>
       </c>
       <c r="G99" t="n">
-        <v>655.08</v>
+        <v>1217.8</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -3225,23 +3213,23 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>695.35</v>
+        <v>253.66</v>
       </c>
       <c r="E100" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F100" t="n">
-        <v>7001</v>
+        <v>2715</v>
       </c>
       <c r="G100" t="n">
-        <v>1217.8</v>
+        <v>490.68</v>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -3253,20 +3241,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>277.23</v>
+        <v>724.11</v>
       </c>
       <c r="E101" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F101" t="n">
-        <v>2887</v>
+        <v>3131</v>
       </c>
       <c r="G101" t="n">
-        <v>490.68</v>
+        <v>1791.53</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -3276,28 +3264,28 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>830.8499999999999</v>
+        <v>8.51</v>
       </c>
       <c r="E102" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>3326</v>
+        <v>717</v>
       </c>
       <c r="G102" t="n">
-        <v>3583.06</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3309,23 +3297,23 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8.51</v>
+        <v>933.71</v>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="F103" t="n">
-        <v>812</v>
+        <v>21786</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>2435.6</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104">
@@ -3337,51 +3325,51 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1043.75</v>
+        <v>147.08</v>
       </c>
       <c r="E104" t="n">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="F104" t="n">
-        <v>23120</v>
+        <v>1826</v>
       </c>
       <c r="G104" t="n">
-        <v>2435.6</v>
+        <v>490.68</v>
       </c>
       <c r="H104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>160.79</v>
+        <v>59.45</v>
       </c>
       <c r="E105" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>2015</v>
+        <v>876</v>
       </c>
       <c r="G105" t="n">
-        <v>1477.12</v>
+        <v>1144.92</v>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3393,23 +3381,23 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>59.45</v>
+        <v>505.87</v>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F106" t="n">
-        <v>912</v>
+        <v>3536</v>
       </c>
       <c r="G106" t="n">
-        <v>1144.92</v>
+        <v>363.56</v>
       </c>
       <c r="H106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3421,23 +3409,23 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>550.24</v>
+        <v>215.99</v>
       </c>
       <c r="E107" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F107" t="n">
-        <v>3815</v>
+        <v>1346</v>
       </c>
       <c r="G107" t="n">
-        <v>363.56</v>
+        <v>981.36</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3449,51 +3437,51 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>215.99</v>
+        <v>179.86</v>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F108" t="n">
-        <v>1484</v>
+        <v>1226</v>
       </c>
       <c r="G108" t="n">
-        <v>981.36</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>228.49</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>1338</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>1791.53</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3505,23 +3493,23 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>574.89</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>5504</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>981.3599999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3533,20 +3521,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>636.3</v>
+        <v>406.92</v>
       </c>
       <c r="E111" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F111" t="n">
-        <v>6129</v>
+        <v>2037</v>
       </c>
       <c r="G111" t="n">
-        <v>1349.16</v>
+        <v>1636.44</v>
       </c>
       <c r="H111" t="n">
         <v>3</v>
@@ -3561,45 +3549,45 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4GQ9HT</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>459.4</v>
+        <v>248.44</v>
       </c>
       <c r="E112" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>2365</v>
+        <v>1897</v>
       </c>
       <c r="G112" t="n">
-        <v>1636.44</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM_Monitor_Arm_B0DB5W4TCP_WM-HA1M-BK_SP_KT (Adaptive Campaign)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0FN4GQ9HT</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>292.37</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>2116</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3612,55 +3600,27 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WM_Monitor_Arm_B0DB5W4TCP_WM-HA1M-BK_SP_KT (Adaptive Campaign)</t>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>2259.25</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>85206</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>2605.02</v>
-      </c>
-      <c r="E115" t="n">
-        <v>78</v>
-      </c>
-      <c r="F115" t="n">
-        <v>91013</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3679,42 +3639,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -3957,13 +3917,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1257.89</v>
+        <v>1123.88</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>46459</v>
+        <v>45402</v>
       </c>
       <c r="G10" t="n">
         <v>4544.92</v>
@@ -3985,13 +3945,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>341.8</v>
+        <v>338.06</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>12312</v>
+        <v>11692</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4069,13 +4029,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2110</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4097,13 +4057,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>574.41</v>
+        <v>566.54</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>20130</v>
+        <v>18403</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4211,47 +4171,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -619,7 +619,7 @@
         <v>177</v>
       </c>
       <c r="F7" t="n">
-        <v>48170</v>
+        <v>48167</v>
       </c>
       <c r="G7" t="n">
         <v>14122.47</v>
@@ -927,7 +927,7 @@
         <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>36753</v>
+        <v>36748</v>
       </c>
       <c r="G18" t="n">
         <v>7046.62</v>
@@ -1291,7 +1291,7 @@
         <v>117</v>
       </c>
       <c r="F31" t="n">
-        <v>6800</v>
+        <v>6796</v>
       </c>
       <c r="G31" t="n">
         <v>13727.12</v>
@@ -1319,7 +1319,7 @@
         <v>117</v>
       </c>
       <c r="F32" t="n">
-        <v>11645</v>
+        <v>11642</v>
       </c>
       <c r="G32" t="n">
         <v>13896.61</v>
@@ -1515,7 +1515,7 @@
         <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6688.25</v>
+        <v>6684.62</v>
       </c>
       <c r="E40" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F40" t="n">
-        <v>59152</v>
+        <v>59138</v>
       </c>
       <c r="G40" t="n">
         <v>13727.12</v>
@@ -1571,7 +1571,7 @@
         <v>17</v>
       </c>
       <c r="F41" t="n">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>92</v>
       </c>
       <c r="F71" t="n">
-        <v>13406</v>
+        <v>13405</v>
       </c>
       <c r="G71" t="n">
         <v>3388.13</v>
@@ -3167,7 +3167,7 @@
         <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="G98" t="n">
         <v>655.08</v>
@@ -3195,7 +3195,7 @@
         <v>44</v>
       </c>
       <c r="F99" t="n">
-        <v>6570</v>
+        <v>6567</v>
       </c>
       <c r="G99" t="n">
         <v>1217.8</v>
@@ -3223,7 +3223,7 @@
         <v>14</v>
       </c>
       <c r="F100" t="n">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="G100" t="n">
         <v>490.68</v>
@@ -3251,7 +3251,7 @@
         <v>33</v>
       </c>
       <c r="F101" t="n">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="G101" t="n">
         <v>1791.53</v>
@@ -3307,7 +3307,7 @@
         <v>96</v>
       </c>
       <c r="F103" t="n">
-        <v>21786</v>
+        <v>21785</v>
       </c>
       <c r="G103" t="n">
         <v>2435.6</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
         <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>7729</v>
+        <v>7193</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -563,7 +563,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>406</v>
+        <v>241</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>814.1900000000001</v>
+        <v>563.21</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>7943</v>
+        <v>4963</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3332.55</v>
+        <v>2170.59</v>
       </c>
       <c r="E7" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="F7" t="n">
-        <v>48167</v>
+        <v>28379</v>
       </c>
       <c r="G7" t="n">
-        <v>14122.47</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>538.24</v>
+        <v>187.52</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>5144</v>
+        <v>2717</v>
       </c>
       <c r="G8" t="n">
-        <v>14617.8</v>
+        <v>7117.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>323.48</v>
+        <v>235.73</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>989</v>
+        <v>603</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>453.96</v>
+        <v>366.34</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>3584</v>
+        <v>2038</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2163.34</v>
+        <v>1597.17</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>25387</v>
+        <v>19859</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>636.36</v>
+        <v>442.8</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>3780</v>
+        <v>3474</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>324.08</v>
+        <v>149.25</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>2061</v>
+        <v>937</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -921,19 +921,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3100.16</v>
+        <v>2077.3</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>36748</v>
+        <v>18546</v>
       </c>
       <c r="G18" t="n">
-        <v>7046.62</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>159.14</v>
+        <v>102.89</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>2909</v>
+        <v>1728</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,22 +1024,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>371.13</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>6077</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Phrase/Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>669.04</v>
+        <v>62.8</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>10035</v>
+        <v>1495</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Phrase/Exact</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>186.9</v>
+        <v>651.4400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F24" t="n">
-        <v>2638</v>
+        <v>5399</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1117,13 +1117,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>984.9200000000001</v>
+        <v>1663.39</v>
       </c>
       <c r="E25" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F25" t="n">
-        <v>7796</v>
+        <v>24702</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1141,17 +1141,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2691.92</v>
+        <v>147.82</v>
       </c>
       <c r="E26" t="n">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>40067</v>
+        <v>1616</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Stand Desk- B0DQ1PKNSP- Broad</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>290.05</v>
+        <v>276.84</v>
       </c>
       <c r="E27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>3064</v>
+        <v>10302</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,50 +1192,50 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-Stand Desk- B0DQ1PKNSP- Broad</t>
+          <t>Camb-SP-Stand Desk-B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>332.79</v>
+        <v>318.81</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
-        <v>11506</v>
+        <v>1252</v>
       </c>
       <c r="G28" t="n">
-        <v>10168.64</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Stand Desk-B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>488.81</v>
+        <v>1474.52</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="F29" t="n">
-        <v>2036</v>
+        <v>7968</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,26 +1257,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2084.43</v>
+        <v>1123.05</v>
       </c>
       <c r="E30" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="F30" t="n">
-        <v>12294</v>
+        <v>4861</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>6863.56</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,26 +1285,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1577.84</v>
+        <v>777.03</v>
       </c>
       <c r="E31" t="n">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="F31" t="n">
-        <v>6796</v>
+        <v>8351</v>
       </c>
       <c r="G31" t="n">
-        <v>13727.12</v>
+        <v>7033.05</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1313,47 +1313,47 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1183.97</v>
+        <v>776.77</v>
       </c>
       <c r="E32" t="n">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="F32" t="n">
-        <v>11642</v>
+        <v>2347</v>
       </c>
       <c r="G32" t="n">
-        <v>13896.61</v>
+        <v>7202.54</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1202.8</v>
+        <v>324.64</v>
       </c>
       <c r="E33" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="F33" t="n">
-        <v>3284</v>
+        <v>1856</v>
       </c>
       <c r="G33" t="n">
-        <v>21251.69</v>
+        <v>12712.71</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1365,20 +1365,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>420.8</v>
+        <v>289.56</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>2856</v>
+        <v>2751</v>
       </c>
       <c r="G34" t="n">
-        <v>12712.71</v>
+        <v>11677.12</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1388,7 +1388,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1397,19 +1397,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>410.56</v>
+        <v>81.3</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>4698</v>
+        <v>1373</v>
       </c>
       <c r="G35" t="n">
-        <v>21845.76</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1421,51 +1421,51 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>153.9</v>
+        <v>48.33</v>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>2754</v>
+        <v>77</v>
       </c>
       <c r="G36" t="n">
-        <v>10778.82</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>48.33</v>
+        <v>850.73</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="F37" t="n">
-        <v>121</v>
+        <v>39665</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>10066.96</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1477,45 +1477,45 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1062.15</v>
+        <v>59.84</v>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>47853</v>
+        <v>1205</v>
       </c>
       <c r="G38" t="n">
-        <v>10066.96</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>96.13999999999999</v>
+        <v>4253.63</v>
       </c>
       <c r="E39" t="n">
-        <v>7</v>
+        <v>298</v>
       </c>
       <c r="F39" t="n">
-        <v>2655</v>
+        <v>44470</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,28 +1528,28 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6684.62</v>
+        <v>220.74</v>
       </c>
       <c r="E40" t="n">
-        <v>443</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>59138</v>
+        <v>1403</v>
       </c>
       <c r="G40" t="n">
-        <v>13727.12</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>325.81</v>
+        <v>20.78</v>
       </c>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>3687</v>
+        <v>190</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1589,51 +1589,51 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20.78</v>
+        <v>105.12</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F42" t="n">
-        <v>303</v>
+        <v>2067</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>7117.8</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>198.31</v>
+        <v>511.17</v>
       </c>
       <c r="E43" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
-        <v>3324</v>
+        <v>1920</v>
       </c>
       <c r="G43" t="n">
-        <v>7117.8</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>666.6900000000001</v>
+        <v>424.02</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F44" t="n">
-        <v>2881</v>
+        <v>2975</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1668,35 +1668,35 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>WB- SP- B0DB5VG39T - CT ref</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>534.51</v>
+        <v>355.84</v>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45" t="n">
-        <v>4429</v>
+        <v>1911</v>
       </c>
       <c r="G45" t="n">
-        <v>7046.62</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - CT ref</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1705,47 +1705,47 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>724.66</v>
+        <v>866.11</v>
       </c>
       <c r="E46" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F46" t="n">
-        <v>5117</v>
+        <v>4703</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1157.57</v>
+        <v>307.63</v>
       </c>
       <c r="E47" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>7357</v>
+        <v>2217</v>
       </c>
       <c r="G47" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>443.63</v>
+        <v>823.85</v>
       </c>
       <c r="E48" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>2940</v>
+        <v>3833</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,162 +1780,162 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1276.77</v>
+        <v>1134.08</v>
       </c>
       <c r="E49" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F49" t="n">
-        <v>5565</v>
+        <v>2366</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>3591.52</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1501.36</v>
+        <v>354.97</v>
       </c>
       <c r="E50" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="F50" t="n">
-        <v>2844</v>
+        <v>304</v>
       </c>
       <c r="G50" t="n">
-        <v>5370.34</v>
+        <v>2456.78</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>378.5</v>
+        <v>559.11</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n">
-        <v>390</v>
+        <v>4091</v>
       </c>
       <c r="G51" t="n">
-        <v>2456.78</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>623.8100000000001</v>
+        <v>560.4300000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F52" t="n">
-        <v>5034</v>
+        <v>4470</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>WB- SP-B0DP3194QN-PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>953.1799999999998</v>
+        <v>201.01</v>
       </c>
       <c r="E53" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="F53" t="n">
-        <v>7953</v>
+        <v>813</v>
       </c>
       <c r="G53" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WB- SP-B0DP3194QN-PT</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>275.83</v>
+        <v>643.6400000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F54" t="n">
-        <v>1291</v>
+        <v>9276</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1948,53 +1948,53 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>720</v>
+        <v>516.24</v>
       </c>
       <c r="E55" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F55" t="n">
-        <v>10245</v>
+        <v>22696</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>549.1700000000001</v>
+        <v>1205.9</v>
       </c>
       <c r="E56" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="F56" t="n">
-        <v>24714</v>
+        <v>20008</v>
       </c>
       <c r="G56" t="n">
-        <v>2626.27</v>
+        <v>1795.76</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -2004,35 +2004,35 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1357.97</v>
+        <v>1835.05</v>
       </c>
       <c r="E57" t="n">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="F57" t="n">
-        <v>23351</v>
+        <v>25842</v>
       </c>
       <c r="G57" t="n">
-        <v>1795.76</v>
+        <v>7416.96</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2041,47 +2041,47 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2241.8</v>
+        <v>434.6</v>
       </c>
       <c r="E58" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="F58" t="n">
-        <v>28486</v>
+        <v>488</v>
       </c>
       <c r="G58" t="n">
-        <v>7416.96</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>863.6499999999999</v>
+        <v>505.54</v>
       </c>
       <c r="E59" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F59" t="n">
-        <v>1015</v>
+        <v>1881</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2791.52</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2093,30 +2093,30 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>723.4000000000001</v>
+        <v>707.4000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F60" t="n">
-        <v>2866</v>
+        <v>2073</v>
       </c>
       <c r="G60" t="n">
-        <v>2791.52</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2125,110 +2125,110 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>903.6700000000001</v>
+        <v>388.94</v>
       </c>
       <c r="E61" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F61" t="n">
-        <v>2720</v>
+        <v>2249</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>3388.14</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>716.37</v>
+        <v>352.43</v>
       </c>
       <c r="E62" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F62" t="n">
-        <v>5155</v>
+        <v>2227</v>
       </c>
       <c r="G62" t="n">
-        <v>5082.209999999999</v>
+        <v>2456.78</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>449.46</v>
+        <v>946.74</v>
       </c>
       <c r="E63" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="F63" t="n">
-        <v>2991</v>
+        <v>4124</v>
       </c>
       <c r="G63" t="n">
-        <v>4913.56</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1407.38</v>
+        <v>1950.51</v>
       </c>
       <c r="E64" t="n">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="F64" t="n">
-        <v>6080</v>
+        <v>5592</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>22111.02</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2237,26 +2237,26 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2879.83</v>
+        <v>1155.64</v>
       </c>
       <c r="E65" t="n">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="F65" t="n">
-        <v>8520</v>
+        <v>2177</v>
       </c>
       <c r="G65" t="n">
-        <v>31972.04</v>
+        <v>2711.02</v>
       </c>
       <c r="H65" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2265,26 +2265,26 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1834.73</v>
+        <v>3328.84</v>
       </c>
       <c r="E66" t="n">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="F66" t="n">
-        <v>3251</v>
+        <v>11823</v>
       </c>
       <c r="G66" t="n">
-        <v>2711.02</v>
+        <v>9827.120000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2293,131 +2293,131 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5027.3</v>
+        <v>2040.82</v>
       </c>
       <c r="E67" t="n">
-        <v>246</v>
+        <v>124</v>
       </c>
       <c r="F67" t="n">
-        <v>18858</v>
+        <v>28186</v>
       </c>
       <c r="G67" t="n">
-        <v>17197.46</v>
+        <v>2456.78</v>
       </c>
       <c r="H67" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2473.27</v>
+        <v>402.01</v>
       </c>
       <c r="E68" t="n">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="F68" t="n">
-        <v>31635</v>
+        <v>10676</v>
       </c>
       <c r="G68" t="n">
-        <v>2456.78</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>402.01</v>
+        <v>1547.42</v>
       </c>
       <c r="E69" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>11232</v>
+        <v>6643</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2215.26</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1714.15</v>
+        <v>1077.14</v>
       </c>
       <c r="E70" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F70" t="n">
-        <v>8925</v>
+        <v>9953</v>
       </c>
       <c r="G70" t="n">
-        <v>2215.26</v>
+        <v>3388.13</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1345.26</v>
+        <v>332.16</v>
       </c>
       <c r="E71" t="n">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="F71" t="n">
-        <v>13405</v>
+        <v>10402</v>
       </c>
       <c r="G71" t="n">
-        <v>3388.13</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2429,17 +2429,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>517.5700000000001</v>
+        <v>338.5</v>
       </c>
       <c r="E72" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F72" t="n">
-        <v>15001</v>
+        <v>1676</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2457,17 +2457,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>416.7</v>
+        <v>184.75</v>
       </c>
       <c r="E73" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
-        <v>2684</v>
+        <v>1840</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2485,17 +2485,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>245.67</v>
+        <v>366.74</v>
       </c>
       <c r="E74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F74" t="n">
-        <v>2684</v>
+        <v>7929</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2523,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2541,17 +2541,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>434.67</v>
+        <v>3.39</v>
       </c>
       <c r="E76" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>10965</v>
+        <v>2293</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,22 +2564,22 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F77" t="n">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,28 +2592,28 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>19.65</v>
+        <v>262.85</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F78" t="n">
-        <v>2809</v>
+        <v>1000</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2625,23 +2625,23 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>172.08</v>
+        <v>305.29</v>
       </c>
       <c r="E79" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F79" t="n">
-        <v>870</v>
+        <v>2627</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>4841.52</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2653,23 +2653,23 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>320.56</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1482</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2681,45 +2681,45 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>483.99</v>
+        <v>35.55</v>
       </c>
       <c r="E81" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>3814</v>
+        <v>561</v>
       </c>
       <c r="G81" t="n">
-        <v>4841.52</v>
+        <v>2626.27</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>526.52</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>15227</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2732,50 +2732,50 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>100.02</v>
+        <v>1227.28</v>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="F83" t="n">
-        <v>875</v>
+        <v>20056</v>
       </c>
       <c r="G83" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>851.11</v>
+        <v>103.72</v>
       </c>
       <c r="E84" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="F84" t="n">
-        <v>18772</v>
+        <v>4881</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2788,91 +2788,91 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1523.41</v>
+        <v>746.1</v>
       </c>
       <c r="E85" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F85" t="n">
-        <v>23549</v>
+        <v>14041</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>195.08</v>
+        <v>1220.39</v>
       </c>
       <c r="E86" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="F86" t="n">
-        <v>8261</v>
+        <v>31084</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>14927.97</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1080.15</v>
+        <v>158.36</v>
       </c>
       <c r="E87" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F87" t="n">
-        <v>21600</v>
+        <v>1272</v>
       </c>
       <c r="G87" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2881,16 +2881,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1777.91</v>
+        <v>461.02</v>
       </c>
       <c r="E88" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F88" t="n">
-        <v>39357</v>
+        <v>6090</v>
       </c>
       <c r="G88" t="n">
-        <v>17143.22</v>
+        <v>6874.58</v>
       </c>
       <c r="H88" t="n">
         <v>3</v>
@@ -2900,22 +2900,22 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>158.36</v>
+        <v>1683.51</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="F89" t="n">
-        <v>2211</v>
+        <v>5853</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2937,41 +2937,41 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>932.27</v>
+        <v>353.02</v>
       </c>
       <c r="E90" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="F90" t="n">
-        <v>12509</v>
+        <v>366</v>
       </c>
       <c r="G90" t="n">
-        <v>9089.83</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2198.2</v>
+        <v>613.02</v>
       </c>
       <c r="E91" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
-        <v>7421</v>
+        <v>476</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2984,22 +2984,22 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>710.29</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>744</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3012,22 +3012,22 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>697.51</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>637</v>
+        <v>25</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3055,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>7</v>
+        <v>147</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,12 +3068,12 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3083,7 +3083,7 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3096,56 +3096,56 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>205.26</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F96" t="n">
-        <v>234</v>
+        <v>1638</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>655.08</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>404.29</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F97" t="n">
-        <v>19</v>
+        <v>4550</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1217.8</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -3157,23 +3157,23 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>285</v>
+        <v>155.72</v>
       </c>
       <c r="E98" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F98" t="n">
-        <v>2430</v>
+        <v>1856</v>
       </c>
       <c r="G98" t="n">
-        <v>655.08</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3185,79 +3185,79 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>650.27</v>
+        <v>545.02</v>
       </c>
       <c r="E99" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F99" t="n">
-        <v>6567</v>
+        <v>2200</v>
       </c>
       <c r="G99" t="n">
-        <v>1217.8</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>253.66</v>
+        <v>8.51</v>
       </c>
       <c r="E100" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>2714</v>
+        <v>576</v>
       </c>
       <c r="G100" t="n">
-        <v>490.68</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>724.11</v>
+        <v>539.29</v>
       </c>
       <c r="E101" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F101" t="n">
-        <v>3130</v>
+        <v>14067</v>
       </c>
       <c r="G101" t="n">
-        <v>1791.53</v>
+        <v>1090.68</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -3269,17 +3269,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8.51</v>
+        <v>58.1</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F102" t="n">
-        <v>717</v>
+        <v>1035</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3292,53 +3292,53 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>933.71</v>
+        <v>46.79</v>
       </c>
       <c r="E103" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>21785</v>
+        <v>560</v>
       </c>
       <c r="G103" t="n">
-        <v>2435.6</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>147.08</v>
+        <v>348.93</v>
       </c>
       <c r="E104" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F104" t="n">
-        <v>1826</v>
+        <v>1950</v>
       </c>
       <c r="G104" t="n">
-        <v>490.68</v>
+        <v>363.56</v>
       </c>
       <c r="H104" t="n">
         <v>1</v>
@@ -3353,23 +3353,23 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>59.45</v>
+        <v>121.26</v>
       </c>
       <c r="E105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F105" t="n">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="G105" t="n">
-        <v>1144.92</v>
+        <v>490.68</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3381,79 +3381,79 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>505.87</v>
+        <v>119.99</v>
       </c>
       <c r="E106" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F106" t="n">
-        <v>3536</v>
+        <v>878</v>
       </c>
       <c r="G106" t="n">
-        <v>363.56</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>215.99</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>1346</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>981.36</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>179.86</v>
+        <v>436.26</v>
       </c>
       <c r="E108" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F108" t="n">
-        <v>1226</v>
+        <v>4284</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>981.3599999999999</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -3465,23 +3465,23 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>252.37</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1145.76</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3493,134 +3493,78 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4GQ9HT</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>574.89</v>
+        <v>145.21</v>
       </c>
       <c r="E110" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F110" t="n">
-        <v>5504</v>
+        <v>1493</v>
       </c>
       <c r="G110" t="n">
-        <v>981.3599999999999</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM_Monitor_Arm_B0DB5W4TCP_WM-HA1M-BK_SP_KT (Adaptive Campaign)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>406.92</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>2037</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>1636.44</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0FN4GQ9HT</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>248.44</v>
+        <v>1405.45</v>
       </c>
       <c r="E112" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F112" t="n">
-        <v>1897</v>
+        <v>54548</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr"/>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>WM_Monitor_Arm_B0DB5W4TCP_WM-HA1M-BK_SP_KT (Adaptive Campaign)</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>2259.25</v>
-      </c>
-      <c r="E114" t="n">
-        <v>70</v>
-      </c>
-      <c r="F114" t="n">
-        <v>85206</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3917,19 +3861,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1123.88</v>
+        <v>799.5</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>45402</v>
+        <v>35233</v>
       </c>
       <c r="G10" t="n">
-        <v>4544.92</v>
+        <v>2329.66</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -3945,13 +3889,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>338.06</v>
+        <v>322.73</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
-        <v>11692</v>
+        <v>9903</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -4057,13 +4001,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>566.54</v>
+        <v>385.7</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>18403</v>
+        <v>13051</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,46 +427,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -507,7 +519,7 @@
         <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>7193</v>
+        <v>7729</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -563,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>241</v>
+        <v>455</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -585,13 +597,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>563.21</v>
+        <v>938.5500000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>4963</v>
+        <v>9830</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -613,19 +625,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2170.59</v>
+        <v>3982.03</v>
       </c>
       <c r="E7" t="n">
-        <v>111</v>
+        <v>206</v>
       </c>
       <c r="F7" t="n">
-        <v>28379</v>
+        <v>57680</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>28188.58</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -641,19 +653,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>187.52</v>
+        <v>710.61</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>2717</v>
+        <v>7900</v>
       </c>
       <c r="G8" t="n">
-        <v>7117.8</v>
+        <v>14617.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -669,13 +681,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>235.73</v>
+        <v>511.4</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>603</v>
+        <v>1270</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -697,13 +709,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>366.34</v>
+        <v>536.72</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>2038</v>
+        <v>4620</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -837,13 +849,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1597.17</v>
+        <v>2356.75</v>
       </c>
       <c r="E15" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>19859</v>
+        <v>27710</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -865,13 +877,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>442.8</v>
+        <v>698.46</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>3474</v>
+        <v>4195</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -893,13 +905,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>149.25</v>
+        <v>341.85</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>937</v>
+        <v>2682</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -921,19 +933,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2077.3</v>
+        <v>3547.11</v>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="F18" t="n">
-        <v>18546</v>
+        <v>54681</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>7046.62</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -949,19 +961,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>102.89</v>
+        <v>176.25</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>1728</v>
+        <v>3449</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>6761.86</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -983,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1001,7 +1013,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1011,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1024,22 +1036,22 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Lshape-Multiple Asins- PT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>371.13</v>
+        <v>59.19</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>6077</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1052,7 +1064,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Phrase/Exact</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1061,13 +1073,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62.8</v>
+        <v>773.1700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F23" t="n">
-        <v>1495</v>
+        <v>14511</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1080,7 +1092,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
+          <t>Camb-SP-Motorized Desk- B0CPT3Q25C- Phrase/Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1089,13 +1101,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>651.4400000000001</v>
+        <v>312.3</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>5399</v>
+        <v>4096</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1108,7 +1120,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C - PT01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1117,13 +1129,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1663.39</v>
+        <v>1083.6</v>
       </c>
       <c r="E25" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>24702</v>
+        <v>8650</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1141,17 +1153,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>147.82</v>
+        <v>2964.29</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="F26" t="n">
-        <v>1616</v>
+        <v>44180</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,7 +1176,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Camb-SP-Stand Desk- B0DQ1PKNSP- Broad</t>
+          <t>Camb-SP-Motorized Desk-B0CPT3Q25C- Exact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,13 +1185,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>276.84</v>
+        <v>401.19</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>10302</v>
+        <v>6344</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,50 +1204,50 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Camb-SP-Stand Desk-B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Stand Desk- B0DQ1PKNSP- Broad</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>318.81</v>
+        <v>421.52</v>
       </c>
       <c r="E28" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
-        <v>1252</v>
+        <v>13370</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>31247.47</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
+          <t>Camb-SP-Stand Desk-B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1474.52</v>
+        <v>579.76</v>
       </c>
       <c r="E29" t="n">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>7968</v>
+        <v>2152</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1260,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- CT ref</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,16 +1269,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1123.05</v>
+        <v>2355.62</v>
       </c>
       <c r="E30" t="n">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="F30" t="n">
-        <v>4861</v>
+        <v>14155</v>
       </c>
       <c r="G30" t="n">
-        <v>6863.56</v>
+        <v>6761.86</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1276,7 +1288,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- PT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,26 +1297,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>777.03</v>
+        <v>1769.67</v>
       </c>
       <c r="E31" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="F31" t="n">
-        <v>8351</v>
+        <v>7665</v>
       </c>
       <c r="G31" t="n">
-        <v>7033.05</v>
+        <v>20760.18</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML- Phrase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1313,47 +1325,47 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>776.77</v>
+        <v>1338.33</v>
       </c>
       <c r="E32" t="n">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="F32" t="n">
-        <v>2347</v>
+        <v>15416</v>
       </c>
       <c r="G32" t="n">
-        <v>7202.54</v>
+        <v>13896.61</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
+          <t>Camb-SP-Zshape-B0CPFS24ML-PT01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>324.64</v>
+        <v>1283.12</v>
       </c>
       <c r="E33" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="F33" t="n">
-        <v>1856</v>
+        <v>3606</v>
       </c>
       <c r="G33" t="n">
-        <v>12712.71</v>
+        <v>14049.15</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1365,20 +1377,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>289.56</v>
+        <v>546.1799999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F34" t="n">
-        <v>2751</v>
+        <v>3567</v>
       </c>
       <c r="G34" t="n">
-        <v>11677.12</v>
+        <v>12712.71</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -1388,7 +1400,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
+          <t>Camb-SP-stand desk- B0DQ1NV8D2- PT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1397,19 +1409,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>81.3</v>
+        <v>466.39</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>1373</v>
+        <v>4829</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>21845.76</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1421,51 +1433,51 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>48.33</v>
+        <v>243.15</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>77</v>
+        <v>2872</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>10778.82</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - PT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>850.73</v>
+        <v>48.33</v>
       </c>
       <c r="E37" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>39665</v>
+        <v>320</v>
       </c>
       <c r="G37" t="n">
-        <v>10066.96</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1477,45 +1489,45 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>59.84</v>
+        <v>1141.7</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="F38" t="n">
-        <v>1205</v>
+        <v>48939</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>10066.96</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
+          <t>Camb-Stand Desk- B0DQ1NV8D2/ B0DQ1PKNSP - Phrase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4253.63</v>
+        <v>119.85</v>
       </c>
       <c r="E39" t="n">
-        <v>298</v>
+        <v>9</v>
       </c>
       <c r="F39" t="n">
-        <v>44470</v>
+        <v>3305</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1528,50 +1540,50 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>Camb-Zshape-Gaming- B0CPFS24ML-Phrase/Exact</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>220.74</v>
+        <v>7589.05</v>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="F40" t="n">
-        <v>1403</v>
+        <v>74566</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>13727.12</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SP_KT_L shape Non Performing Ex</t>
+          <t>SP CT PT_B0CPFS24ML_Gaming</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20.78</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1589,45 +1601,45 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>105.12</v>
+        <v>386.78</v>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F42" t="n">
-        <v>2067</v>
+        <v>5700</v>
       </c>
       <c r="G42" t="n">
-        <v>7117.8</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>511.17</v>
+        <v>20.78</v>
       </c>
       <c r="E43" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>1920</v>
+        <v>408</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,7 +1652,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SP_PT_L shape Non Performing PT</t>
+          <t>SP_KT_L shape Non Performing Ex</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1649,41 +1661,41 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>424.02</v>
+        <v>276.92</v>
       </c>
       <c r="E44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>2975</v>
+        <v>4285</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>7117.8</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - CT ref</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>355.84</v>
+        <v>805.9</v>
       </c>
       <c r="E45" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F45" t="n">
-        <v>1911</v>
+        <v>3476</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1696,25 +1708,25 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5VG39T - PT</t>
+          <t>SP_PT_L shape Non Performing PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>866.11</v>
+        <v>612.65</v>
       </c>
       <c r="E46" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F46" t="n">
-        <v>4703</v>
+        <v>6058</v>
       </c>
       <c r="G46" t="n">
-        <v>2626.27</v>
+        <v>7046.62</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -1724,22 +1736,22 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WB- SP- B0DB5VG39T - CT ref</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>307.63</v>
+        <v>886.78</v>
       </c>
       <c r="E47" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F47" t="n">
-        <v>2217</v>
+        <v>6250</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1752,137 +1764,137 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
+          <t>WB- SP- B0DB5VG39T - PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>823.85</v>
+        <v>1360.08</v>
       </c>
       <c r="E48" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="F48" t="n">
-        <v>3833</v>
+        <v>8758</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2VVRND - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1134.08</v>
+        <v>536.3099999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="F49" t="n">
-        <v>2366</v>
+        <v>3316</v>
       </c>
       <c r="G49" t="n">
-        <v>3591.52</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP2WC5VW - PT</t>
+          <t>WB- SP- B0DB5YTQZV-B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>354.97</v>
+        <v>1415.94</v>
       </c>
       <c r="E50" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="F50" t="n">
-        <v>304</v>
+        <v>6385</v>
       </c>
       <c r="G50" t="n">
-        <v>2456.78</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WB- SP- B0DP32F346 - PT</t>
+          <t>WB- SP- B0DP2VVRND - PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>559.11</v>
+        <v>1720.33</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="F51" t="n">
-        <v>4091</v>
+        <v>3253</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>7149.15</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WB- SP-B0DB5W4TCP-PT</t>
+          <t>WB- SP- B0DP2WC5VW - PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>560.4300000000001</v>
+        <v>443.77</v>
       </c>
       <c r="E52" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F52" t="n">
-        <v>4470</v>
+        <v>435</v>
       </c>
       <c r="G52" t="n">
-        <v>1355.08</v>
+        <v>2456.78</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -1892,22 +1904,22 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WB- SP-B0DP3194QN-PT</t>
+          <t>WB- SP- B0DP32F346 - PT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>201.01</v>
+        <v>739.58</v>
       </c>
       <c r="E53" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>813</v>
+        <v>5898</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1920,7 +1932,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
+          <t>WB- SP-B0DB5W4TCP-PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1929,26 +1941,26 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>643.6400000000001</v>
+        <v>1146.29</v>
       </c>
       <c r="E54" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="F54" t="n">
-        <v>9276</v>
+        <v>9825</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
+          <t>WB- SP-B0DP3194QN-PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1957,138 +1969,138 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>516.24</v>
+        <v>334.18</v>
       </c>
       <c r="E55" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F55" t="n">
-        <v>22696</v>
+        <v>1517</v>
       </c>
       <c r="G55" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
+          <t>WM- Adj Metal desk- B0DB5W4TCP-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1205.9</v>
+        <v>720</v>
       </c>
       <c r="E56" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F56" t="n">
-        <v>20008</v>
+        <v>10245</v>
       </c>
       <c r="G56" t="n">
-        <v>1795.76</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
+          <t>WM- Heavy-Duty Mechanical- B0DP3194QN - SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1835.05</v>
+        <v>549.1700000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="F57" t="n">
-        <v>25842</v>
+        <v>24719</v>
       </c>
       <c r="G57" t="n">
-        <v>7416.96</v>
+        <v>2626.27</v>
       </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
+          <t>WM- Height Adj stand - B0DP2VVRND-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>434.6</v>
+        <v>1357.97</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="F58" t="n">
-        <v>488</v>
+        <v>23351</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1795.76</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- Height Adj stand Dual-B0DB5YTQZV-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>505.54</v>
+        <v>2241.8</v>
       </c>
       <c r="E59" t="n">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="F59" t="n">
-        <v>1881</v>
+        <v>28487</v>
       </c>
       <c r="G59" t="n">
-        <v>2791.52</v>
+        <v>7416.96</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
+          <t>WM- Height Adjustable stand- Dual-B0DB5YTQZV- PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2097,13 +2109,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>707.4000000000001</v>
+        <v>1037.19</v>
       </c>
       <c r="E60" t="n">
         <v>27</v>
       </c>
       <c r="F60" t="n">
-        <v>2073</v>
+        <v>1158</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2116,91 +2128,91 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>388.94</v>
+        <v>823.9300000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F61" t="n">
-        <v>2249</v>
+        <v>3196</v>
       </c>
       <c r="G61" t="n">
-        <v>3388.14</v>
+        <v>2791.52</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
+          <t>WM- SP- Adj Metal desk- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>352.43</v>
+        <v>948.9</v>
       </c>
       <c r="E62" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>2227</v>
+        <v>3101</v>
       </c>
       <c r="G62" t="n">
-        <v>2456.78</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
+          <t>WM- SP- Height Adjustable stand- Dual-B0DB5YTQZV- Broad</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>946.74</v>
+        <v>863.24</v>
       </c>
       <c r="E63" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="F63" t="n">
-        <v>4124</v>
+        <v>6910</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>5082.209999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
+          <t>WM- SP- Wall Mounted Stand- B0DP2WC5VW- Broad</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2209,54 +2221,54 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1950.51</v>
+        <v>642.67</v>
       </c>
       <c r="E64" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F64" t="n">
-        <v>5592</v>
+        <v>4021</v>
       </c>
       <c r="G64" t="n">
-        <v>22111.02</v>
+        <v>4913.56</v>
       </c>
       <c r="H64" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
+          <t>WM- SP- Wooden Arm- B0DP32F346- PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1155.64</v>
+        <v>1564.94</v>
       </c>
       <c r="E65" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F65" t="n">
-        <v>2177</v>
+        <v>6604</v>
       </c>
       <c r="G65" t="n">
-        <v>2711.02</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM- SP-Wall Mounted Stand- B0DP2WC5VW- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2265,26 +2277,26 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3328.84</v>
+        <v>3358.73</v>
       </c>
       <c r="E66" t="n">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="F66" t="n">
-        <v>11823</v>
+        <v>9963</v>
       </c>
       <c r="G66" t="n">
-        <v>9827.120000000001</v>
+        <v>34428.82</v>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2293,16 +2305,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2040.82</v>
+        <v>2114.52</v>
       </c>
       <c r="E67" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F67" t="n">
-        <v>28186</v>
+        <v>3660</v>
       </c>
       <c r="G67" t="n">
-        <v>2456.78</v>
+        <v>2711.02</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
@@ -2312,53 +2324,53 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>402.01</v>
+        <v>5776.28</v>
       </c>
       <c r="E68" t="n">
-        <v>19</v>
+        <v>291</v>
       </c>
       <c r="F68" t="n">
-        <v>10676</v>
+        <v>22791</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>24567.8</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
+          <t>WM- Wall Mounted Stand- B0DP2WC5VW- SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1547.42</v>
+        <v>2473.27</v>
       </c>
       <c r="E69" t="n">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="F69" t="n">
-        <v>6643</v>
+        <v>31640</v>
       </c>
       <c r="G69" t="n">
-        <v>2215.26</v>
+        <v>2456.78</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -2368,35 +2380,35 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
+          <t>WM- Wooden Arm- B0DP32F346-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1077.14</v>
+        <v>402.01</v>
       </c>
       <c r="E70" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F70" t="n">
-        <v>9953</v>
+        <v>11232</v>
       </c>
       <c r="G70" t="n">
-        <v>3388.13</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-Gas Spring MA- B0DB5VG39T-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2405,26 +2417,26 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>332.16</v>
+        <v>1714.15</v>
       </c>
       <c r="E71" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="F71" t="n">
-        <v>10402</v>
+        <v>8925</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>2215.26</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
+          <t>WM-Gas Spring MA- Dual - B0DB5VVPSB-SP-KT-Phrase/BM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2433,19 +2445,19 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>338.5</v>
+        <v>1345.26</v>
       </c>
       <c r="E72" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="F72" t="n">
-        <v>1676</v>
+        <v>13406</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>3388.13</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2457,17 +2469,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>184.75</v>
+        <v>517.5700000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F73" t="n">
-        <v>1840</v>
+        <v>15400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2485,17 +2497,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>366.74</v>
+        <v>416.7</v>
       </c>
       <c r="E74" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F74" t="n">
-        <v>7929</v>
+        <v>2793</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2513,17 +2525,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>320.26</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>2785</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2541,17 +2553,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>2293</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2564,22 +2576,22 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>85.93000000000001</v>
+        <v>451.26</v>
       </c>
       <c r="E77" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F77" t="n">
-        <v>549</v>
+        <v>11125</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,56 +2604,56 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>262.85</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="G78" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - AT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>305.29</v>
+        <v>19.65</v>
       </c>
       <c r="E79" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>2627</v>
+        <v>2811</v>
       </c>
       <c r="G79" t="n">
-        <v>4841.52</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2653,17 +2665,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>172.08</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>894</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2681,20 +2693,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>35.55</v>
+        <v>331.04</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>561</v>
+        <v>1559</v>
       </c>
       <c r="G81" t="n">
-        <v>2626.27</v>
+        <v>1694.07</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
@@ -2704,50 +2716,50 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>526.52</v>
+        <v>569.13</v>
       </c>
       <c r="E82" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F82" t="n">
-        <v>15227</v>
+        <v>4726</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>4841.52</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1227.28</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>20056</v>
+        <v>54</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2760,106 +2772,106 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - CT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>103.72</v>
+        <v>100.02</v>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F84" t="n">
-        <v>4881</v>
+        <v>1129</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>2626.27</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>746.1</v>
+        <v>918.95</v>
       </c>
       <c r="E85" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F85" t="n">
-        <v>14041</v>
+        <v>19486</v>
       </c>
       <c r="G85" t="n">
-        <v>2626.27</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Monitor Arms- Multi Asins - exact</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1220.39</v>
+        <v>1670.5</v>
       </c>
       <c r="E86" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F86" t="n">
-        <v>31084</v>
+        <v>25073</v>
       </c>
       <c r="G86" t="n">
-        <v>14927.97</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>158.36</v>
+        <v>195.08</v>
       </c>
       <c r="E87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F87" t="n">
-        <v>1272</v>
+        <v>8438</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2872,35 +2884,35 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
+          <t>WM-SP- Premium Monitor Arms- Multi Asins -Phrase</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>461.02</v>
+        <v>1182.5</v>
       </c>
       <c r="E88" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F88" t="n">
-        <v>6090</v>
+        <v>22663</v>
       </c>
       <c r="G88" t="n">
-        <v>6874.58</v>
+        <v>2626.27</v>
       </c>
       <c r="H88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2909,41 +2921,41 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1683.51</v>
+        <v>1899.13</v>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="F89" t="n">
-        <v>5853</v>
+        <v>40103</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>17143.22</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Gas Spring -Multi Asins- Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>353.02</v>
+        <v>186.53</v>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F90" t="n">
-        <v>366</v>
+        <v>2709</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2956,50 +2968,50 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Broad</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>613.02</v>
+        <v>1362.54</v>
       </c>
       <c r="E91" t="n">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="F91" t="n">
-        <v>476</v>
+        <v>18730</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>9089.83</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T- Exact &amp; Phrase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2335.67</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>8570</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3012,22 +3024,22 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>710.29</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F93" t="n">
-        <v>25</v>
+        <v>802</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3040,22 +3052,22 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
+          <t>WM-SP-Gas Spring MA- B0DB5VG39T/B0DB5VVPSB- PT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>748.1800000000001</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F94" t="n">
-        <v>147</v>
+        <v>726</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3068,22 +3080,22 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WM-SP-POS stand- Multi - PT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - PT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0FN4FPJ83</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>221.91</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>16</v>
+        <v>737</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3096,78 +3108,78 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 - Phrase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>205.26</v>
+        <v>171.98</v>
       </c>
       <c r="E96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F96" t="n">
-        <v>1638</v>
+        <v>276</v>
       </c>
       <c r="G96" t="n">
-        <v>655.08</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-Monitor Stand-B0DP2Z5DQ9 -Phrase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>404.29</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="E97" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F97" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="G97" t="n">
-        <v>1217.8</v>
+        <v>2388.98</v>
       </c>
       <c r="H97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
+          <t>WM-SP-POS stand- Multi - PT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4FPJ83</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>155.72</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>1856</v>
+        <v>20</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3185,114 +3197,114 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>545.02</v>
+        <v>299.29</v>
       </c>
       <c r="E99" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F99" t="n">
-        <v>2200</v>
+        <v>2621</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>655.08</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8.51</v>
+        <v>695.35</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="F100" t="n">
-        <v>576</v>
+        <v>7001</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1217.8</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>539.29</v>
+        <v>277.23</v>
       </c>
       <c r="E101" t="n">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>14067</v>
+        <v>2887</v>
       </c>
       <c r="G101" t="n">
-        <v>1090.68</v>
+        <v>490.68</v>
       </c>
       <c r="H101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
+          <t>WM-SP-TV Brackets- Multi Asins- CT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>58.1</v>
+        <v>830.8499999999999</v>
       </c>
       <c r="E102" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="F102" t="n">
-        <v>1035</v>
+        <v>3326</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>3583.06</v>
       </c>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3301,13 +3313,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>46.79</v>
+        <v>8.51</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>560</v>
+        <v>812</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3320,7 +3332,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3329,26 +3341,26 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>348.93</v>
+        <v>1043.75</v>
       </c>
       <c r="E104" t="n">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="F104" t="n">
-        <v>1950</v>
+        <v>23120</v>
       </c>
       <c r="G104" t="n">
-        <v>363.56</v>
+        <v>2435.6</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
+          <t>WM-SP-TV Brackets- Multi Asins- Exact</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3357,19 +3369,19 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>121.26</v>
+        <v>160.79</v>
       </c>
       <c r="E105" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F105" t="n">
-        <v>896</v>
+        <v>2015</v>
       </c>
       <c r="G105" t="n">
-        <v>490.68</v>
+        <v>1477.12</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
@@ -3381,76 +3393,76 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FN4HDM6Z</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>119.99</v>
+        <v>59.45</v>
       </c>
       <c r="E106" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>878</v>
+        <v>912</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1144.92</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0FHVWHQHR</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>550.24</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>3815</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>363.56</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0FN4D3C89</t>
+          <t>B0FN4DSQ6P</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>436.26</v>
+        <v>215.99</v>
       </c>
       <c r="E108" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F108" t="n">
-        <v>4284</v>
+        <v>1484</v>
       </c>
       <c r="G108" t="n">
-        <v>981.3599999999999</v>
+        <v>981.36</v>
       </c>
       <c r="H108" t="n">
         <v>2</v>
@@ -3460,28 +3472,28 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0FN4DSQ6P</t>
+          <t>B0FN4HDM6Z</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>252.37</v>
+        <v>228.49</v>
       </c>
       <c r="E109" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F109" t="n">
-        <v>1450</v>
+        <v>1338</v>
       </c>
       <c r="G109" t="n">
-        <v>1145.76</v>
+        <v>1791.53</v>
       </c>
       <c r="H109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3493,17 +3505,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0FN4GQ9HT</t>
+          <t>B0FHVWHQHR</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>145.21</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>1493</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3516,55 +3528,139 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WM_Monitor_Arm_B0DB5W4TCP_WM-HA1M-BK_SP_KT (Adaptive Campaign)</t>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FN4D3C89</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>636.3</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>6129</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1349.16</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>B0FN4DSQ6P</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>459.4</v>
+      </c>
+      <c r="E112" t="n">
+        <v>27</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2365</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1636.44</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>WM-SP-TV Brackets- Multi Asins- PT01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>B0FN4GQ9HT</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>292.37</v>
+      </c>
+      <c r="E113" t="n">
+        <v>18</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2116</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>WM_Monitor_Arm_B0DB5W4TCP_WM-HA1M-BK_SP_KT (Adaptive Campaign)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>WM_SP_KT_Adjustable_Exact_Manual_HV</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>B0CPT3Q25C</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>1405.45</v>
-      </c>
-      <c r="E112" t="n">
-        <v>44</v>
-      </c>
-      <c r="F112" t="n">
-        <v>54548</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
+      <c r="D115" t="n">
+        <v>2605.02</v>
+      </c>
+      <c r="E115" t="n">
+        <v>78</v>
+      </c>
+      <c r="F115" t="n">
+        <v>91013</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3583,42 +3679,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -3861,19 +3957,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>799.5</v>
+        <v>1257.89</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
-        <v>35233</v>
+        <v>46459</v>
       </c>
       <c r="G10" t="n">
-        <v>2329.66</v>
+        <v>4544.92</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3889,13 +3985,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>322.73</v>
+        <v>341.8</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>9903</v>
+        <v>12312</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3973,13 +4069,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2110</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4001,13 +4097,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>385.7</v>
+        <v>574.41</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
-        <v>13051</v>
+        <v>20130</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -4115,47 +4211,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -3679,42 +3667,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4211,47 +4199,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -4195,7 +4195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4430,117 +4430,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3. WM - Desk - Manual</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>B0CPT3Q25C</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2362</v>
-      </c>
-      <c r="E7" t="n">
-        <v>45</v>
-      </c>
-      <c r="F7" t="n">
-        <v>295.8679633333333</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4237.57</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3. WM - Desk - Manual</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>B0DQ1NV8D2</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2362</v>
-      </c>
-      <c r="E8" t="n">
-        <v>45</v>
-      </c>
-      <c r="F8" t="n">
-        <v>295.8679633333333</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4237.57</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3. WM - Desk - Manual</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B0DQ4YWSMC</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2362</v>
-      </c>
-      <c r="E9" t="n">
-        <v>45</v>
-      </c>
-      <c r="F9" t="n">
-        <v>295.8679633333333</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4237.57</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -3667,42 +3679,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4199,47 +4211,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -3679,42 +3667,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4211,47 +4199,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week21.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -3667,42 +3679,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4199,47 +4211,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
